--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104504_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104504_W6.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0869</v>
+        <v>7.5724</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6739</v>
+        <v>6.3481</v>
       </c>
       <c r="F2" t="n">
-        <v>5.413</v>
+        <v>1.2243</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2728</v>
+        <v>7.0182</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6841</v>
+        <v>3.6682</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5887</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4777</v>
+        <v>7.5029</v>
       </c>
       <c r="K2" t="n">
-        <v>2.403</v>
+        <v>3.7124</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>3.7905</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7952</v>
+        <v>-0.4847</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2811</v>
+        <v>-0.0442</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5141</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5231</v>
+        <v>-0.3077</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8501</v>
+        <v>-0.1258</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.1819</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06419999999999999</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3856</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4498</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8845</v>
+        <v>6.6039</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1374</v>
+        <v>1.3032</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7471</v>
+        <v>5.3007</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3692</v>
+        <v>4.269</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4892</v>
+        <v>2.6717</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.12</v>
+        <v>1.5972</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2091</v>
+        <v>2.4457</v>
       </c>
       <c r="K3" t="n">
-        <v>2.625</v>
+        <v>2.3712</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4159</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1601</v>
+        <v>1.8233</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8641</v>
+        <v>0.3005</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>1.5228</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3831</v>
+        <v>2.0359</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0302</v>
+        <v>1.5208</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4133</v>
+        <v>0.5151</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7712</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.539</v>
+        <v>6.5005</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6975</v>
+        <v>2.1251</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8416</v>
+        <v>4.3754</v>
       </c>
       <c r="G4" t="n">
-        <v>7.0315</v>
+        <v>3.3607</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6783</v>
+        <v>3.4814</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3532</v>
+        <v>-0.1207</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5471</v>
+        <v>2.1811</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7435</v>
+        <v>2.606</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8036</v>
+        <v>-0.4249</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5157</v>
+        <v>1.1796</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0653</v>
+        <v>0.8754</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4504</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3583</v>
+        <v>1.0001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8347</v>
+        <v>-0.0073</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5235</v>
+        <v>1.0074</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1596</v>
+        <v>4.8158</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0413</v>
+        <v>-0.2307</v>
       </c>
       <c r="F5" t="n">
-        <v>5.201</v>
+        <v>5.0466</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1483</v>
+        <v>2.1474</v>
       </c>
       <c r="H5" t="n">
-        <v>1.554</v>
+        <v>1.5593</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4787</v>
+        <v>0.4531</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0838</v>
+        <v>1.0719</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6052</v>
+        <v>-0.6188</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6697</v>
+        <v>1.6942</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0587</v>
+        <v>0.6017</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.868</v>
+        <v>-0.019</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8093</v>
+        <v>0.6207</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0219</v>
+        <v>2.6388</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9245</v>
+        <v>2.6128</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0974</v>
+        <v>0.026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2599</v>
+        <v>0.2614</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1746</v>
+        <v>-0.1752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4345</v>
+        <v>0.4365</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3702</v>
+        <v>1.3518</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6611</v>
+        <v>0.6443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1103</v>
+        <v>-1.0904</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4649</v>
+        <v>0.1498</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5383</v>
+        <v>0.1716</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0735</v>
+        <v>-0.0218</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.892</v>
+        <v>1.2853</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9513</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8433</v>
+        <v>1.8947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4621</v>
+        <v>0.4606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.798</v>
+        <v>0.7957</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3359</v>
+        <v>-0.3351</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3752</v>
+        <v>-0.3872</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8373</v>
+        <v>0.8477</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2241</v>
+        <v>0.1615</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1905</v>
+        <v>0.1648</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2797</v>
+        <v>-0.7336</v>
       </c>
       <c r="E8" t="n">
-        <v>0.176</v>
+        <v>-0.6674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1036</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8366</v>
+        <v>-1.8371</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2234</v>
+        <v>-1.2198</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7612</v>
+        <v>-1.7485</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3354</v>
+        <v>-1.3315</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>1.638</v>
+        <v>0.6271</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2249</v>
+        <v>0.4016</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4131</v>
+        <v>0.2254</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9103</v>
+        <v>-1.0507</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2185</v>
+        <v>-2.2509</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3081</v>
+        <v>1.2002</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0058</v>
+        <v>-1.4235</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5957</v>
+        <v>0.8903</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4101</v>
+        <v>-2.3137</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.5077</v>
+        <v>-1.5095</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9967</v>
+        <v>1.5373</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.511</v>
+        <v>-3.0469</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5019</v>
+        <v>0.0861</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.599</v>
+        <v>-0.6471</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1009</v>
+        <v>0.7331</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5934</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2232</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.7025</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.8147</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1881</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1966</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.008500000000000001</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.0927</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.0927</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9219</v>
+        <v>-1.1804</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.716</v>
+        <v>-3.7594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7941</v>
+        <v>2.579</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4169</v>
+        <v>-5.0268</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8888</v>
+        <v>-3.6067</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3057</v>
+        <v>-1.42</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4821</v>
+        <v>-5.543</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5514</v>
+        <v>-3.0174</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.0335</v>
+        <v>-2.5255</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.5162</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6626</v>
+        <v>-0.5893</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7277</v>
+        <v>1.1055</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2516</v>
+        <v>0.9359</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0998</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1518</v>
+        <v>0.2418</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.7071</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9864</v>
+        <v>-1.9843</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7447</v>
+        <v>-1.6342</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2417</v>
+        <v>-0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2972</v>
+        <v>-2.292</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1141</v>
+        <v>-0.1067</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1831</v>
+        <v>-2.1854</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3969</v>
+        <v>-1.4042</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9003</v>
+        <v>-0.8879</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0502</v>
+        <v>-0.058</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2976</v>
+        <v>0.1721</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1886</v>
+        <v>-4.9144</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0053</v>
+        <v>-4.9106</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1833</v>
+        <v>-0.0039</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4197</v>
+        <v>-2.412</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6681</v>
+        <v>-1.6659</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7516</v>
+        <v>-0.746</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7681</v>
+        <v>-0.7781</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.88</v>
+        <v>-0.8898</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6516</v>
+        <v>-1.6339</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0892</v>
+        <v>0.3657</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.8564</v>
+        <v>19.5533</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.067799999999998</v>
+        <v>-1.673399999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>20.9242</v>
+        <v>21.2268</v>
       </c>
       <c r="G13" t="n">
-        <v>4.567599999999999</v>
+        <v>4.525900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>6.926699999999999</v>
+        <v>6.894799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.358999999999999</v>
+        <v>-2.3689</v>
       </c>
       <c r="J13" t="n">
-        <v>4.477400000000001</v>
+        <v>4.224</v>
       </c>
       <c r="K13" t="n">
-        <v>8.5161</v>
+        <v>8.338700000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0388</v>
+        <v>-4.1146</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09029999999999894</v>
+        <v>0.3017000000000005</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5896</v>
+        <v>-1.4439</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6797</v>
+        <v>1.7458</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5367</v>
+        <v>4.552700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1467</v>
+        <v>18.2105</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4137</v>
+        <v>6.132000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6617</v>
+        <v>3.3877</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7521</v>
+        <v>2.7442</v>
       </c>
       <c r="V13" t="n">
-        <v>4.338400000000001</v>
+        <v>4.343000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4032</v>
+        <v>4.3728</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.06470000000000009</v>
+        <v>-0.02979999999999994</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.23</v>
+        <v>2.5621</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2111</v>
+        <v>0.874</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0189</v>
+        <v>1.6882</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6321</v>
+        <v>0.6296</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0244</v>
+        <v>0.0312</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6077</v>
+        <v>0.5984</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1418</v>
+        <v>1.1024</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3019</v>
+        <v>1.282</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1601</v>
+        <v>-0.1796</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5097</v>
+        <v>-0.4728</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2774</v>
+        <v>-1.2508</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.2739</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2521</v>
+        <v>-0.544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6478</v>
+        <v>0.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.792</v>
+        <v>1.6851</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6907</v>
+        <v>-0.8323</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4827</v>
+        <v>2.5174</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2696</v>
+        <v>-0.2624</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1229</v>
+        <v>-0.1071</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1467</v>
+        <v>-0.1553</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6125</v>
+        <v>-0.6342</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2641</v>
+        <v>1.2583</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8767</v>
+        <v>-1.8925</v>
       </c>
       <c r="M15" t="n">
-        <v>0.343</v>
+        <v>0.3718</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.387</v>
+        <v>-1.3654</v>
       </c>
       <c r="O15" t="n">
-        <v>1.73</v>
+        <v>1.7372</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1406</v>
+        <v>-0.2589</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2389</v>
+        <v>-0.3558</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0983</v>
+        <v>0.0969</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1481</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6343</v>
+        <v>-1.215</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5138</v>
+        <v>1.285</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2897</v>
+        <v>2.0374</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3781</v>
+        <v>0.8754</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9116</v>
+        <v>1.162</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.145</v>
+        <v>2.7959</v>
       </c>
       <c r="K16" t="n">
-        <v>0.159</v>
+        <v>1.7237</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3039</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1447</v>
+        <v>-0.7585</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5371</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6077</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5059</v>
+        <v>-0.3692</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8207</v>
+        <v>-0.4324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3149</v>
+        <v>0.0631</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.6876</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>-1.0746</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4923</v>
+        <v>-0.0736</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6486</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1563</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0237</v>
+        <v>-1.2853</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8641</v>
+        <v>-0.3736</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1595</v>
+        <v>-0.9116</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8112</v>
+        <v>-0.1688</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7317</v>
+        <v>0.1444</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0795</v>
+        <v>-0.3132</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7875</v>
+        <v>-1.1164</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8675</v>
+        <v>-0.518</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08</v>
+        <v>-0.5984</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0.2799</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9043</v>
+        <v>0.4085</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0297</v>
+        <v>-0.1286</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6747</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.0603</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5539</v>
+        <v>-2.6592</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9393</v>
+        <v>-3.4527</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3854</v>
+        <v>0.7935</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3782</v>
+        <v>0.3722</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2451</v>
+        <v>-1.2546</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6233</v>
+        <v>1.6268</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8309</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4094</v>
+        <v>-0.4351</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4812</v>
+        <v>-0.4587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4785</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1693</v>
+        <v>-0.6415</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3091</v>
+        <v>0.0653</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6082</v>
+        <v>-2.9454</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4964</v>
+        <v>-2.7048</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1118</v>
+        <v>-0.2406</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2095</v>
+        <v>1.7535</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3245</v>
+        <v>0.6955</v>
       </c>
       <c r="I19" t="n">
-        <v>0.885</v>
+        <v>1.058</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1212</v>
+        <v>1.7949</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1212</v>
+        <v>1.1991</v>
       </c>
       <c r="L19" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.0414</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.5036</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4622</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-4.325</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.7803</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.3739</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.4967</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.0883</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.2033</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1.1342</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1.361</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2268</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.6589</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.4174</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-1.2415</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-2.0246</v>
-      </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8316</v>
+        <v>-3.007</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.249</v>
+        <v>-1.3871</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5826</v>
+        <v>-1.6199</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7546</v>
+        <v>1.2265</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7043</v>
+        <v>0.3354</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0503</v>
+        <v>0.8911</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8226</v>
+        <v>0.1207</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2255</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5971</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.068</v>
+        <v>1.1058</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5212</v>
+        <v>0.2148</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4532</v>
+        <v>0.8911</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.3098</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.7635</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2763</v>
+        <v>-1.0742</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4688</v>
+        <v>-0.2998</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8075</v>
+        <v>-0.7744</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0896</v>
+        <v>-3.8048</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4908</v>
+        <v>-3.5052</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5988</v>
+        <v>-0.2996</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1895</v>
+        <v>-1.1789</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2295</v>
+        <v>-1.2238</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7321</v>
+        <v>-0.7168</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8586</v>
+        <v>-0.5772</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3115</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5471</v>
+        <v>-0.2658</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>A. PLUMMER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5296</v>
+        <v>-4.227</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7256</v>
+        <v>-3.3087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.196</v>
+        <v>-0.9183</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9964</v>
+        <v>-2.814</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.6792</v>
+        <v>-1.1782</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3171</v>
+        <v>-1.6358</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9189</v>
+        <v>-2.7276</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.9936</v>
+        <v>-0.3587</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>-2.3689</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0774</v>
+        <v>-0.0863</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6857</v>
+        <v>-0.8194</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3918</v>
+        <v>0.7331</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4649</v>
+        <v>-0.7608</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2208</v>
+        <v>-0.3534</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6856</v>
+        <v>-0.4074</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2249</v>
+        <v>-1.5628</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PLUMMER</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9213</v>
+        <v>-4.8773</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5291</v>
+        <v>-4.886</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3922</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8205</v>
+        <v>-5.0045</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1892</v>
+        <v>-4.695</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6313</v>
+        <v>-0.3095</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7125</v>
+        <v>-2.9537</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3534</v>
+        <v>-3.0282</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3591</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.108</v>
+        <v>-2.0508</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8357</v>
+        <v>-1.6668</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7277</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4333</v>
+        <v>0.1288</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5898</v>
+        <v>-0.3373</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8435</v>
+        <v>0.4661</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5748</v>
+        <v>-0.2292</v>
       </c>
       <c r="W23" t="n">
+        <v>-0.2292</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-1.5748</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.8564</v>
+        <v>-17.2771</v>
       </c>
       <c r="E24" t="n">
-        <v>-20.9241</v>
+        <v>-21.2268</v>
       </c>
       <c r="F24" t="n">
-        <v>2.067699999999999</v>
+        <v>3.949799999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.567600000000001</v>
+        <v>-4.5259</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.9267</v>
+        <v>-6.8948</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3591</v>
+        <v>2.369000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0900000000000003</v>
+        <v>-0.3016000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5897</v>
+        <v>1.444100000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6798</v>
+        <v>-1.7456</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.4773</v>
+        <v>-4.2241</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.5161</v>
+        <v>-8.3386</v>
       </c>
       <c r="O24" t="n">
-        <v>4.0388</v>
+        <v>4.1147</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.536700000000001</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-18.1466</v>
+        <v>-18.2105</v>
       </c>
       <c r="R24" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.4137</v>
+        <v>-3.8555</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.7522</v>
+        <v>-2.7444</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.6616</v>
+        <v>-1.1115</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.3383</v>
+        <v>-4.342999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.06460000000000005</v>
+        <v>0.02979999999999997</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.403</v>
+        <v>-4.3728</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104504_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104504_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-0.02979999999999994</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104504_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.3728</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
